--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588145.2371542891</v>
+        <v>588145</v>
       </c>
       <c r="R2" t="n">
-        <v>6343798.717851379</v>
+        <v>6343799</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-05-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1980-05-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42795-2025 artfynd.xlsx
+++ b/artfynd/A 42795-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74552734</v>
       </c>
       <c r="B2" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
